--- a/modelo-semanal.xlsx
+++ b/modelo-semanal.xlsx
@@ -525,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C23"/>
+  <dimension ref="B2:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -621,135 +621,147 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
+    <row r="12" ht="14" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
+          <t>Negrito nos textos</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Escreva **assim** para deixar em negrito no painel. Vale no insight e nas duas notas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
           <t>Célula em branco</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Deixe vazia quando o dado não existir. A tela mostra “sem dado” em cinza e conta no selo do topo. Nunca preencha com zero para tapar buraco: zero é uma afirmação, vazio é a verdade.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>direcao</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>menor = quanto menor melhor (rotatividade). maior = quanto maior melhor (treinamento). Vazio = não sabemos o que é melhorar; o cartão fica cinza e as setas não julgam. É o caso de Admitidos enquanto a regra não estiver definida.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>direcao</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>menor = quanto menor melhor (rotatividade). maior = quanto maior melhor (treinamento). Vazio = não sabemos o que é melhorar; o cartão fica cinza e as setas não julgam. É o caso de Admitidos enquanto a regra não estiver definida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
           <t>estado</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>auto deixa o painel calcular o farol: conta quantas comparações disponíveis estão piores. Nenhuma pior = verde; até metade = amarelo; mais da metade = vermelho. Para sobrepor, escreva bom, atencao, critico ou nd.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>taxa e qtd</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>taxa é o percentual sobre o headcount; qtd é o número de pessoas. Os dois aparecem lado a lado no cartão.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>SERIE</t>
+          <t>taxa e qtd</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Uma linha por indicador, um mês por coluna, na ordem. Meses ainda não fechados ficam em branco — a linha de tendência simplesmente para ali.</t>
+          <t>taxa é o percentual sobre o headcount; qtd é o número de pessoas. Os dois aparecem lado a lado no cartão.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="B17" s="4" t="inlineStr">
         <is>
+          <t>SERIE</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Uma linha por indicador, um mês por coluna, na ordem. Meses ainda não fechados ficam em branco — a linha de tendência simplesmente para ali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
           <t>MOTIVOS</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>O painel mostra os três primeiros de cada família. Separe voluntário de involuntário: “por que nos deixam” e “por que desligamos” são conversas diferentes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>O painel mostra os três primeiros de cada família. Separe voluntário de involuntário: “por que nos deixam” e “por que desligamos” são conversas diferentes. O percentual de cada motivo é calculado sobre o total de desligamentos daquele tipo (vem do bloco KPI), não sobre a soma dos três.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>DIRETORIAS</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>taxa e indice ficam em branco enquanto não houver headcount por diretoria. Sem eles o ranking é de tamanho, não de risco — a tela avisa isso sozinha.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>A logo</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="42" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
+    <row r="21" ht="42" customHeight="1">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Trocar a logo</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>No painel, botão Trocar logo, escolha o arquivo (PNG, JPG ou SVG). Ela é embutida no HTML, então continua aparecendo mesmo com o arquivo fora da rede. Depois use Salvar semana para gravar o painel já com a logo.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Publicação</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Pasta de rede</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>O arquivo é autossuficiente: não busca nada na internet, não usa fonte externa, não faz chamada de rede. Abre por duplo clique ou por caminho de rede.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
+          <t>Pasta de rede</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>O arquivo é autossuficiente: não busca nada na internet, não usa fonte externa, não faz chamada de rede. Abre por duplo clique ou por caminho de rede.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
           <t>Para o PPT</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>A tela é 16:9. Dê um print da área do painel e cole no slide — encaixa sem sobra. Ou use Imprimir / PDF, que já sai em paisagem só com o painel.</t>
         </is>
@@ -766,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O45"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -856,173 +868,132 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
+          <t>janela</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Mês (MTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
           <t>regua</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>MTD com 4 de 4,4 semanas</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>#KPI</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="7" t="n"/>
-      <c r="O8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="7" t="n"/>
+      <c r="M9" s="7" t="n"/>
+      <c r="N9" s="7" t="n"/>
+      <c r="O9" s="7" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>titulo</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>taxa</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>qtd</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>unidade</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>sem_qtd</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>sem_taxa</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>mes_ant_rotulo</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>mes_ant</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>media_atual</t>
         </is>
       </c>
-      <c r="K9" s="10" t="inlineStr">
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>media_ant</t>
         </is>
       </c>
-      <c r="L9" s="10" t="inlineStr">
+      <c r="L10" s="10" t="inlineStr">
         <is>
           <t>direcao</t>
         </is>
       </c>
-      <c r="M9" s="10" t="inlineStr">
+      <c r="M10" s="10" t="inlineStr">
         <is>
           <t>estado</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>turnover</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Turnover geral</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>91</v>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>saídas</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>Junho</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>123</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>119</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>105</v>
-      </c>
-      <c r="L10" s="9" t="inlineStr">
-        <is>
-          <t>menor</t>
-        </is>
-      </c>
-      <c r="M10" s="9" t="inlineStr">
-        <is>
-          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>voluntario</t>
+          <t>turnover</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Voluntários</t>
+          <t>Turnover geral</t>
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>0.92</v>
+        <v>1.7</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
@@ -1030,10 +1001,10 @@
         </is>
       </c>
       <c r="F11" s="9" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0.13</v>
+        <v>0.36</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
@@ -1041,13 +1012,13 @@
         </is>
       </c>
       <c r="I11" s="9" t="n">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>75.3</v>
+        <v>119</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>74.59999999999999</v>
+        <v>105</v>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
@@ -1063,19 +1034,19 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>involuntario</t>
+          <t>voluntario</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Involuntários</t>
+          <t>Voluntários</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
@@ -1083,10 +1054,10 @@
         </is>
       </c>
       <c r="F12" s="9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
@@ -1094,13 +1065,13 @@
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>43.5</v>
+        <v>75.3</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>32.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="L12" s="9" t="inlineStr">
         <is>
@@ -1116,378 +1087,382 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
+          <t>involuntario</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Involuntários</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>saídas</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>menor</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
           <t>admitidos</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Admitidos</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C14" s="9" t="n">
         <v>1.46</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D14" s="9" t="n">
         <v>78</v>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>entradas</t>
         </is>
       </c>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Junho</t>
         </is>
       </c>
-      <c r="I13" s="9" t="n">
+      <c r="I14" s="9" t="n">
         <v>85</v>
       </c>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="9" t="n"/>
-      <c r="L13" s="9" t="inlineStr"/>
-      <c r="M13" s="9" t="inlineStr">
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="9" t="n"/>
+      <c r="L14" s="9" t="inlineStr"/>
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>#SERIE</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
-      <c r="N15" s="7" t="n"/>
-      <c r="O15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="7" t="n"/>
+      <c r="N16" s="7" t="n"/>
+      <c r="O16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>jan</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>fev</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>mar</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>abr</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>mai</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>jun</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>jul</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>ago</t>
         </is>
       </c>
-      <c r="J16" s="10" t="inlineStr">
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>set</t>
         </is>
       </c>
-      <c r="K16" s="10" t="inlineStr">
+      <c r="K17" s="10" t="inlineStr">
         <is>
           <t>out</t>
         </is>
       </c>
-      <c r="L16" s="10" t="inlineStr">
+      <c r="L17" s="10" t="inlineStr">
         <is>
           <t>nov</t>
         </is>
       </c>
-      <c r="M16" s="10" t="inlineStr">
+      <c r="M17" s="10" t="inlineStr">
         <is>
           <t>dez</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>turnover</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>93</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>147</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>116</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>119</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>115</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>123</v>
-      </c>
-      <c r="H17" s="9" t="n">
-        <v>91</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>voluntario</t>
+          <t>turnover</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>63</v>
+        <v>147</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>involuntario</t>
+          <t>voluntario</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>34</v>
+        <v>82</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>37</v>
+        <v>82</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
+          <t>involuntario</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>84</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>37</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
           <t>admitidos</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>#PERFIL</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="7" t="n"/>
+      <c r="K23" s="7" t="n"/>
+      <c r="L23" s="7" t="n"/>
+      <c r="M23" s="7" t="n"/>
+      <c r="N23" s="7" t="n"/>
+      <c r="O23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>titulo</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>pct_rotulo</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>incidencia_rotulo</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>incidencia</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>mes_ant_rotulo</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>mes_ant</t>
         </is>
       </c>
-      <c r="J23" s="10" t="inlineStr">
+      <c r="J24" s="10" t="inlineStr">
         <is>
           <t>media_atual</t>
         </is>
       </c>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>media_ant</t>
         </is>
       </c>
-      <c r="L23" s="10" t="inlineStr">
+      <c r="L24" s="10" t="inlineStr">
         <is>
           <t>direcao</t>
         </is>
       </c>
-      <c r="M23" s="10" t="inlineStr">
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>estado</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>lideres</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>Líderes desligados</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>das saídas</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>Taxa sobre líderes</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>Junho</t>
-        </is>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
-      <c r="L24" s="9" t="inlineStr">
-        <is>
-          <t>menor</t>
-        </is>
-      </c>
-      <c r="M24" s="9" t="inlineStr">
-        <is>
-          <t>auto</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>ate1ano</t>
+          <t>lideres</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Até 1 ano</t>
+          <t>Líderes desligados</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>35.2</v>
+        <v>9.9</v>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
@@ -1496,7 +1471,7 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Taxa de incidência</t>
+          <t>Taxa sobre líderes</t>
         </is>
       </c>
       <c r="G25" s="9" t="n"/>
@@ -1505,7 +1480,9 @@
           <t>Junho</t>
         </is>
       </c>
-      <c r="I25" s="9" t="n"/>
+      <c r="I25" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="inlineStr">
@@ -1519,58 +1496,90 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>ate1ano</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Até 1 ano</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>das saídas</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Taxa de incidência</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>Junho</t>
+        </is>
+      </c>
+      <c r="I26" s="9" t="n"/>
+      <c r="J26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>menor</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>#MOTIVOS</t>
         </is>
       </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="7" t="n"/>
-      <c r="L27" s="7" t="n"/>
-      <c r="M27" s="7" t="n"/>
-      <c r="N27" s="7" t="n"/>
-      <c r="O27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
+      <c r="I28" s="7" t="n"/>
+      <c r="J28" s="7" t="n"/>
+      <c r="K28" s="7" t="n"/>
+      <c r="L28" s="7" t="n"/>
+      <c r="M28" s="7" t="n"/>
+      <c r="N28" s="7" t="n"/>
+      <c r="O28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>familia</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>motivo</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>qtd</t>
         </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Voluntário</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>Particular</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="30">
@@ -1581,11 +1590,11 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Proposta externa</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
@@ -1596,26 +1605,26 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Mudança de cidade</t>
+          <t>Proposta externa</t>
         </is>
       </c>
       <c r="C31" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Involuntário</t>
+          <t>Voluntário</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mudança de cidade</t>
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1626,11 +1635,11 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Cultura organizacional</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="C33" s="9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34">
@@ -1641,110 +1650,104 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Redução de quadro</t>
+          <t>Cultura organizacional</t>
         </is>
       </c>
       <c r="C34" s="9" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Involuntário</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Redução de quadro</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>#DIRETORIAS</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
-      <c r="I36" s="7" t="n"/>
-      <c r="J36" s="7" t="n"/>
-      <c r="K36" s="7" t="n"/>
-      <c r="L36" s="7" t="n"/>
-      <c r="M36" s="7" t="n"/>
-      <c r="N36" s="7" t="n"/>
-      <c r="O36" s="7" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="7" t="n"/>
+      <c r="I37" s="7" t="n"/>
+      <c r="J37" s="7" t="n"/>
+      <c r="K37" s="7" t="n"/>
+      <c r="L37" s="7" t="n"/>
+      <c r="M37" s="7" t="n"/>
+      <c r="N37" s="7" t="n"/>
+      <c r="O37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>sigla</t>
         </is>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>vol</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>inv</t>
         </is>
       </c>
-      <c r="D37" s="10" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="E37" s="10" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>pct</t>
         </is>
       </c>
-      <c r="F37" s="10" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>taxa</t>
         </is>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>indice</t>
         </is>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>FLO</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="C38" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>61</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>67</v>
-      </c>
-      <c r="F38" s="9" t="n"/>
-      <c r="G38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>FLO</t>
         </is>
       </c>
       <c r="B39" s="9" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C39" s="9" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="E39" s="9" t="n">
-        <v>13.2</v>
+        <v>67</v>
       </c>
       <c r="F39" s="9" t="n"/>
       <c r="G39" s="9" t="n"/>
@@ -1752,79 +1755,100 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>TRP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B40" s="9" t="n">
         <v>6</v>
       </c>
       <c r="C40" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E40" s="9" t="n">
-        <v>7.7</v>
+        <v>13.2</v>
       </c>
       <c r="F40" s="9" t="n"/>
       <c r="G40" s="9" t="n"/>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>TRP</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>#TEXTO</t>
         </is>
       </c>
-      <c r="B42" s="7" t="n"/>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
-      <c r="G42" s="7" t="n"/>
-      <c r="H42" s="7" t="n"/>
-      <c r="I42" s="7" t="n"/>
-      <c r="J42" s="7" t="n"/>
-      <c r="K42" s="7" t="n"/>
-      <c r="L42" s="7" t="n"/>
-      <c r="M42" s="7" t="n"/>
-      <c r="N42" s="7" t="n"/>
-      <c r="O42" s="7" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>insight</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>Julho: volume desacelera 26% vs junho, puxado pelo voluntário (−37%). Atenção no involuntário — igual à média de 2026, mas +28% acima da média de 2025. Alerta nos líderes: 9 saídas contra 4 em junho.</t>
-        </is>
-      </c>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="7" t="n"/>
+      <c r="I43" s="7" t="n"/>
+      <c r="J43" s="7" t="n"/>
+      <c r="K43" s="7" t="n"/>
+      <c r="L43" s="7" t="n"/>
+      <c r="M43" s="7" t="n"/>
+      <c r="N43" s="7" t="n"/>
+      <c r="O43" s="7" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>nota_motivos</t>
+          <t>insight</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>“Particular” = 82% dos pedidos de demissão. O motivo mais frequente é “não sabemos”: achado de codificação, não de visualização.</t>
+          <t>**Julho:** volume desacelera 26% vs junho, puxado pelo voluntário (−37%). **Atenção no involuntário** — igual à média de 2026, mas **+28% acima da média de 2025**. **Alerta nos líderes:** 9 saídas contra 4 em junho.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
+          <t>nota_motivos</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>**“Particular” = 82% dos pedidos de demissão.** O motivo mais frequente é “não sabemos”: achado de codificação, não de visualização.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
           <t>nota_diretorias</t>
         </is>
       </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Ranking de tamanho, não de risco. Falta headcount por diretoria para calcular taxa e índice de sobre-representação.</t>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>**Ranking de tamanho, não de risco.** Falta headcount por diretoria para calcular taxa e índice de sobre-representação.</t>
         </is>
       </c>
     </row>
@@ -1892,11 +1916,11 @@
         </is>
       </c>
       <c r="C5" s="13">
-        <f>'Dados'!D11+'Dados'!D12</f>
+        <f>'Dados'!D12+'Dados'!D13</f>
         <v/>
       </c>
       <c r="D5" s="13">
-        <f>'Dados'!D10</f>
+        <f>'Dados'!D11</f>
         <v/>
       </c>
       <c r="E5" s="12">
@@ -1911,11 +1935,11 @@
         </is>
       </c>
       <c r="C6" s="13">
-        <f>'Dados'!F11+'Dados'!F12</f>
+        <f>'Dados'!F12+'Dados'!F13</f>
         <v/>
       </c>
       <c r="D6" s="13">
-        <f>'Dados'!F10</f>
+        <f>'Dados'!F11</f>
         <v/>
       </c>
       <c r="E6" s="12">
@@ -1934,7 +1958,7 @@
         <v/>
       </c>
       <c r="D7" s="13">
-        <f>'Dados'!D11</f>
+        <f>'Dados'!D12</f>
         <v/>
       </c>
       <c r="E7" s="12">
@@ -1953,7 +1977,7 @@
         <v/>
       </c>
       <c r="D8" s="13">
-        <f>'Dados'!D12</f>
+        <f>'Dados'!D13</f>
         <v/>
       </c>
       <c r="E8" s="12">
@@ -1968,11 +1992,11 @@
         </is>
       </c>
       <c r="C9" s="13">
-        <f>SUM('Dados'!D38:D40)</f>
+        <f>SUM('Dados'!D39:D41)</f>
         <v/>
       </c>
       <c r="D9" s="13">
-        <f>'Dados'!D10</f>
+        <f>'Dados'!D11</f>
         <v/>
       </c>
       <c r="E9" s="12">
@@ -1987,7 +2011,7 @@
         </is>
       </c>
       <c r="C10" s="13">
-        <f>SUM('Dados'!B17:M17)</f>
+        <f>SUM('Dados'!B18:M18)</f>
         <v/>
       </c>
       <c r="D10" s="14" t="n"/>
